--- a/見積/数量表_大藪小_計装設備.xlsx
+++ b/見積/数量表_大藪小_計装設備.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -519,7 +519,7 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>923</v>
+        <v>1006</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -528,7 +528,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>b 個別リモコン 433m＋h 室内機～室外機 490m</t>
+          <t>b 個別リモコン 472m＋h 室内機～室外機 534m</t>
         </is>
       </c>
     </row>
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
@@ -558,7 +558,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>a 集中リモコン 110m＋d 遠隔監視 9m</t>
+          <t>a 集中リモコン 120m＋d 遠隔監視 10m</t>
         </is>
       </c>
     </row>
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
@@ -699,7 +699,7 @@
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
@@ -895,17 +895,17 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
+          <t>別途</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
           <t>空調制御盤</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>空調制御盤 ＳＲ－１</t>
-        </is>
-      </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>自立形 Ｗ６００×Ｄ２００×Ｈ１０００ 架台Ｈ７００</t>
+          <t>（別途）</t>
         </is>
       </c>
       <c r="D18" s="4" t="n">
@@ -913,29 +913,29 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>面</t>
+          <t>式</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>鋼板製焼付塗装・鍵No.200、運転リモコン3・ON/OFFコントローラー2・停電時運転盤（自立運転切換SW）組込</t>
+          <t>SR-1・SR-2（Kの指示で別途）</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>空調制御盤</t>
+          <t>別途</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>空調制御盤 ＳＲ－２</t>
+          <t>計装試験調整</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>自立形 Ｗ６００×Ｄ２００×Ｈ１０００ 架台Ｈ７００</t>
+          <t>（別途）</t>
         </is>
       </c>
       <c r="D19" s="4" t="n">
@@ -943,38 +943,12 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>面</t>
+          <t>式</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>運転リモコン1 組込</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>試験調整</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>計装試験調整</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr"/>
-      <c r="D20" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>式</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>2人工</t>
+          <t>Kの指示で別途</t>
         </is>
       </c>
     </row>
@@ -2173,30 +2147,30 @@
       <c r="A42" s="4" t="inlineStr"/>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>計 ×1.1（余長）→見積数量</t>
+          <t>計 ×1.2（余長）→見積数量</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr"/>
       <c r="D42" s="4" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>433</v>
+        <v>472</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H42" s="4" t="n">
         <v>3</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>490</v>
+        <v>534</v>
       </c>
       <c r="K42" s="4" t="inlineStr"/>
     </row>

--- a/見積/数量表_大藪小_計装設備.xlsx
+++ b/見積/数量表_大藪小_計装設備.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -678,7 +678,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>室外機置場 a・d・h（GP-28）</t>
+          <t>① M-20 室外機置場 a・d・h（置場入口～GHP-1～4）</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>室外機置場 f・g 自立ユニット～GHP-1～4</t>
+          <t>② M-20 f・g 自立ユニット～GHP-1～4</t>
         </is>
       </c>
     </row>
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>d・e 遠隔監視アダプタ廻り</t>
+          <t>③ M-20 d・e GHP-1～遠隔監視アダプタ</t>
         </is>
       </c>
     </row>
@@ -750,16 +750,16 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>薄鋼電線管</t>
+          <t>厚鋼電線管</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Ｅ６０ 屋内露出</t>
+          <t>Ｇ７０ 屋外露出</t>
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>7.2</v>
+        <v>3</v>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
@@ -768,7 +768,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>SR-1 引込 a×2・b×3・c×3</t>
+          <t>④ M-17 SR-1 引込 屋外PB～冷媒管共巻き a×2・b×3・c×3</t>
         </is>
       </c>
     </row>
@@ -780,16 +780,16 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>薄鋼電線管</t>
+          <t>ねじなし電線管</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Ｅ２５ 屋内露出</t>
+          <t>Ｅ６３ 屋内露出</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>3.6</v>
+        <v>8</v>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>SR-2 立下り</t>
+          <t>⑤ M-17 SR-1 引込 屋内PB～SR-1 a×2・b×3・c×3（図面の E60 は無い規格）</t>
         </is>
       </c>
     </row>
@@ -810,25 +810,25 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>プルボックス</t>
+          <t>ねじなし電線管</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>２５０×２５０×２５０ ＳＵＳ製ＷＰ</t>
+          <t>Ｅ２５ 屋内露出</t>
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>個</t>
+          <t>ｍ</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>SR-1 引込 屋外側</t>
+          <t>⑥ M-18 SR-2 立下り</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>２５０×２５０×２５０ 錆止塗装</t>
+          <t>２５０×２５０×２５０ ＳＵＳ製ＷＰ</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
@@ -858,7 +858,7 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>SR-1 引込 屋内側</t>
+          <t>⑦ M-17 SR-1 引込 屋外側</t>
         </is>
       </c>
     </row>
@@ -870,12 +870,12 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>コア抜き</t>
+          <t>プルボックス</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>φ１００程度</t>
+          <t>２５０×２５０×２５０ 錆止塗装</t>
         </is>
       </c>
       <c r="D17" s="4" t="n">
@@ -883,29 +883,29 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>か所</t>
+          <t>個</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>★印 SR-1 引込</t>
+          <t>⑧ M-17 SR-1 引込 屋内側</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>別途</t>
+          <t>電線管・ボックス</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>空調制御盤</t>
+          <t>コア抜き</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>（別途）</t>
+          <t>φ１００程度</t>
         </is>
       </c>
       <c r="D18" s="4" t="n">
@@ -913,12 +913,12 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>式</t>
+          <t>か所</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>SR-1・SR-2（Kの指示で別途）</t>
+          <t>⑨ M-17 ★印 SR-1 引込</t>
         </is>
       </c>
     </row>
@@ -930,23 +930,53 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
+          <t>空調制御盤</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>（別途）</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>式</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>SR-1・SR-2（Kの指示で別途）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>別途</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
           <t>計装試験調整</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>（別途）</t>
         </is>
       </c>
-      <c r="D19" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="D20" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>式</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>Kの指示で別途</t>
         </is>

--- a/見積/数量表_大藪小_計装設備.xlsx
+++ b/見積/数量表_大藪小_計装設備.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -648,7 +648,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>e 遠隔監視アダプタ電源（管内）</t>
+          <t>e 遠隔監視アダプタ電源（冷媒管共巻き）</t>
         </is>
       </c>
     </row>
@@ -665,11 +665,11 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Ｇ２８ 屋外露出</t>
+          <t>Ｇ７０ 屋外露出</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>① M-20 室外機置場 a・d・h（置場入口～GHP-1～4）</t>
+          <t>① M-17 SR-1 引込 屋外PB～冷媒管共巻き a×2・b×3・c×3</t>
         </is>
       </c>
     </row>
@@ -690,16 +690,16 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>厚鋼電線管</t>
+          <t>ねじなし電線管</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Ｇ３６ 屋外露出</t>
+          <t>Ｅ６３ 屋内露出</t>
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>② M-20 f・g 自立ユニット～GHP-1～4</t>
+          <t>② M-17 SR-1 引込 屋内PB～SR-1 a×2・b×3・c×3（図面の E60 は無い規格）</t>
         </is>
       </c>
     </row>
@@ -720,16 +720,16 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>厚鋼電線管</t>
+          <t>ねじなし電線管</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Ｇ２２ 屋外露出</t>
+          <t>Ｅ２５ 屋内露出</t>
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>③ M-20 d・e GHP-1～遠隔監視アダプタ</t>
+          <t>③ M-18 SR-2 立下り</t>
         </is>
       </c>
     </row>
@@ -750,25 +750,25 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>厚鋼電線管</t>
+          <t>プルボックス</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Ｇ７０ 屋外露出</t>
+          <t>２５０×２５０×２５０ ＳＵＳ製ＷＰ</t>
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>ｍ</t>
+          <t>個</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>④ M-17 SR-1 引込 屋外PB～冷媒管共巻き a×2・b×3・c×3</t>
+          <t>④ M-17 SR-1 引込 屋外側</t>
         </is>
       </c>
     </row>
@@ -780,25 +780,25 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>ねじなし電線管</t>
+          <t>プルボックス</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Ｅ６３ 屋内露出</t>
+          <t>２５０×２５０×２５０ 錆止塗装</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>ｍ</t>
+          <t>個</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>⑤ M-17 SR-1 引込 屋内PB～SR-1 a×2・b×3・c×3（図面の E60 は無い規格）</t>
+          <t>⑤ M-17 SR-1 引込 屋内側</t>
         </is>
       </c>
     </row>
@@ -810,42 +810,42 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>ねじなし電線管</t>
+          <t>コア抜き</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Ｅ２５ 屋内露出</t>
+          <t>φ１００程度</t>
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>ｍ</t>
+          <t>か所</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>⑥ M-18 SR-2 立下り</t>
+          <t>⑥ M-17 ★印 SR-1 引込</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>電線管・ボックス</t>
+          <t>別途</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>プルボックス</t>
+          <t>空調制御盤</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>２５０×２５０×２５０ ＳＵＳ製ＷＰ</t>
+          <t>（別途）</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
@@ -853,29 +853,29 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>個</t>
+          <t>式</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>⑦ M-17 SR-1 引込 屋外側</t>
+          <t>SR-1・SR-2（Kの指示で別途）</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>電線管・ボックス</t>
+          <t>別途</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>プルボックス</t>
+          <t>計装試験調整</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>２５０×２５０×２５０ 錆止塗装</t>
+          <t>（別途）</t>
         </is>
       </c>
       <c r="D17" s="4" t="n">
@@ -883,100 +883,10 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>個</t>
+          <t>式</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>⑧ M-17 SR-1 引込 屋内側</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>電線管・ボックス</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>コア抜き</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>φ１００程度</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>か所</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>⑨ M-17 ★印 SR-1 引込</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>別途</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>空調制御盤</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>（別途）</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>式</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>SR-1・SR-2（Kの指示で別途）</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>別途</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>計装試験調整</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>（別途）</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>式</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>Kの指示で別途</t>
         </is>

--- a/見積/数量表_大藪小_計装設備.xlsx
+++ b/見積/数量表_大藪小_計装設備.xlsx
@@ -510,12 +510,12 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>ケーブル</t>
+          <t>ケーブルEM-CEE1.25-2C</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>ＥＭ－ＣＥＥ１．２５sq－２Ｃ</t>
+          <t>ころがし（冷媒管共巻き・天井内）</t>
         </is>
       </c>
       <c r="D5" s="4" t="n">
@@ -540,12 +540,12 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>ケーブル</t>
+          <t>ケーブルEM-CEES1.25-2C</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>ＥＭ－ＣＥＥＳ１．２５sq－２Ｃ</t>
+          <t>ころがし（冷媒管共巻き・天井内）</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
@@ -570,16 +570,16 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>ケーブル</t>
+          <t>ケーブルEM-CEES1.25-6C</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>ＥＭ－ＣＥＥＳ１．２５sq－７Ｃ</t>
+          <t>ころがし（冷媒管共巻き・天井内）</t>
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>181</v>
+        <v>18</v>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
@@ -588,7 +588,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>c 室外機～自立運転切替SW</t>
+          <t>f 自立信号線</t>
         </is>
       </c>
     </row>
@@ -600,16 +600,16 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>ケーブル</t>
+          <t>ケーブルEM-CEES1.25-7C</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>ＥＭ－ＣＥＥＳ１．２５sq－６Ｃ</t>
+          <t>ころがし（冷媒管共巻き・天井内）</t>
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>18</v>
+        <v>181</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
@@ -618,7 +618,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>f 自立信号線</t>
+          <t>c 室外機～自立運転切替SW</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>ケーブル</t>
+          <t>ケーブルEM-CE2.0-3C</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>ＥＭ－ＣＥ２sq－３Ｃ</t>
+          <t>ころがし（冷媒管共巻き・天井内）</t>
         </is>
       </c>
       <c r="D9" s="4" t="n">
@@ -660,16 +660,16 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>厚鋼電線管</t>
+          <t>電線管　E25</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Ｇ７０ 屋外露出</t>
+          <t>EP-25 屋内露出（SR-2立下り）</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>① M-17 SR-1 引込 屋外PB～冷媒管共巻き a×2・b×3・c×3</t>
+          <t>③ M-18 SR-2 立下り</t>
         </is>
       </c>
     </row>
@@ -690,12 +690,12 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>ねじなし電線管</t>
+          <t>電線管　E63</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Ｅ６３ 屋内露出</t>
+          <t>EP-63 屋内露出（SR-1引込）</t>
         </is>
       </c>
       <c r="D11" s="4" t="n">
@@ -708,7 +708,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>② M-17 SR-1 引込 屋内PB～SR-1 a×2・b×3・c×3（図面の E60 は無い規格）</t>
+          <t>② M-17 SR-1 引込 屋内PB～SR-1 a×2・b×3・c×3</t>
         </is>
       </c>
     </row>
@@ -720,16 +720,16 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>ねじなし電線管</t>
+          <t>溶融亜鉛メッキ電線管　G70</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Ｅ２５ 屋内露出</t>
+          <t>GP-70 屋外露出（SR-1引込）</t>
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>③ M-18 SR-2 立下り</t>
+          <t>① M-17 SR-1 引込 屋外PB～冷媒管共巻き a×2・b×3・c×3</t>
         </is>
       </c>
     </row>
@@ -750,12 +750,12 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>プルボックス</t>
+          <t>プルボックス250×250×250</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>２５０×２５０×２５０ ＳＵＳ製ＷＰ</t>
+          <t>錆止め（SR-1引込 屋内側）</t>
         </is>
       </c>
       <c r="D13" s="4" t="n">
@@ -768,7 +768,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>④ M-17 SR-1 引込 屋外側</t>
+          <t>⑤ M-17 SR-1 引込 屋内側</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>プルボックス</t>
+          <t>機械はつり</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>２５０×２５０×２５０ 錆止塗装</t>
+          <t>φ100 200mm（SR-1引込）</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
@@ -793,12 +793,12 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>個</t>
+          <t>か所</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>⑤ M-17 SR-1 引込 屋内側</t>
+          <t>⑥ M-17 ★印 SR-1 引込</t>
         </is>
       </c>
     </row>
@@ -810,12 +810,12 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>コア抜き</t>
+          <t>防水プルボックス250×250×250SUS</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>φ１００程度</t>
+          <t>屋外側（SR-1引込）</t>
         </is>
       </c>
       <c r="D15" s="4" t="n">
@@ -823,12 +823,12 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>か所</t>
+          <t>個</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>⑥ M-17 ★印 SR-1 引込</t>
+          <t>④ M-17 SR-1 引込 屋外側</t>
         </is>
       </c>
     </row>

--- a/見積/数量表_大藪小_計装設備.xlsx
+++ b/見積/数量表_大藪小_計装設備.xlsx
@@ -750,7 +750,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>プルボックス250×250×250</t>
+          <t>プルボックス250×250×200</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -810,7 +810,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>防水プルボックス250×250×250SUS</t>
+          <t>防水プルボックス250×250×200SUS</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">

--- a/見積/数量表_大藪小_計装設備.xlsx
+++ b/見積/数量表_大藪小_計装設備.xlsx
@@ -810,7 +810,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>防水プルボックス250×250×200SUS</t>
+          <t>防水プルボックス300×300×200SUS</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">

--- a/見積/数量表_大藪小_計装設備.xlsx
+++ b/見積/数量表_大藪小_計装設備.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -505,90 +505,78 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>計装配線</t>
+          <t>自動制御盤・調整</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>ケーブルEM-CEE1.25-2C</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>ころがし（冷媒管共巻き・天井内）</t>
-        </is>
-      </c>
+          <t>SR-1自動制御盤</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr"/>
       <c r="D5" s="4" t="n">
-        <v>1006</v>
+        <v>1</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>ｍ</t>
+          <t>面</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>b 個別リモコン 472m＋h 室内機～室外機 534m</t>
+          <t>輪之内中 2,877,000×0.65（Kの指示で輪之内中と同額）</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>計装配線</t>
+          <t>自動制御盤・調整</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>ケーブルEM-CEES1.25-2C</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>ころがし（冷媒管共巻き・天井内）</t>
-        </is>
-      </c>
+          <t>SR-2自動制御盤</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr"/>
       <c r="D6" s="4" t="n">
-        <v>130</v>
+        <v>1</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>ｍ</t>
+          <t>面</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>a 集中リモコン 120m＋d 遠隔監視 10m</t>
+          <t>輪之内中 2,731,000×0.65（Kの指示で輪之内中と同額）</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>計装配線</t>
+          <t>自動制御盤・調整</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>ケーブルEM-CEES1.25-6C</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>ころがし（冷媒管共巻き・天井内）</t>
-        </is>
-      </c>
+          <t>調整費</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr"/>
       <c r="D7" s="4" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>ｍ</t>
+          <t>式</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>f 自立信号線</t>
+          <t>輪之内中 842,000×0.65（Kの指示で輪之内中と同額）</t>
         </is>
       </c>
     </row>
@@ -600,7 +588,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>ケーブルEM-CEES1.25-7C</t>
+          <t>ケーブルEM-CEE1.25-2C</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -609,7 +597,7 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>181</v>
+        <v>1006</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
@@ -618,7 +606,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>c 室外機～自立運転切替SW</t>
+          <t>b 個別リモコン 472m＋h 室内機～室外機 534m</t>
         </is>
       </c>
     </row>
@@ -630,7 +618,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>ケーブルEM-CE2.0-3C</t>
+          <t>ケーブルEM-CEES1.25-2C</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -639,7 +627,7 @@
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>3</v>
+        <v>130</v>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
@@ -648,28 +636,28 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>e 遠隔監視アダプタ電源（冷媒管共巻き）</t>
+          <t>a 集中リモコン 120m＋d 遠隔監視 10m</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>電線管・ボックス</t>
+          <t>計装配線</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>電線管　E25</t>
+          <t>ケーブルEM-CEES1.25-6C</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>EP-25 屋内露出（SR-2立下り）</t>
+          <t>ころがし（冷媒管共巻き・天井内）</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
@@ -678,28 +666,28 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>③ M-18 SR-2 立下り</t>
+          <t>f 自立信号線</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>電線管・ボックス</t>
+          <t>計装配線</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>電線管　E63</t>
+          <t>ケーブルEM-CEES1.25-7C</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>EP-63 屋内露出（SR-1引込）</t>
+          <t>ころがし（冷媒管共巻き・天井内）</t>
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>8</v>
+        <v>181</v>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
@@ -708,24 +696,24 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>② M-17 SR-1 引込 屋内PB～SR-1 a×2・b×3・c×3</t>
+          <t>c 室外機～自立運転切替SW</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>電線管・ボックス</t>
+          <t>計装配線</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>溶融亜鉛メッキ電線管　G70</t>
+          <t>ケーブルEM-CE2.0-3C</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>GP-70 屋外露出（SR-1引込）</t>
+          <t>ころがし（冷媒管共巻き・天井内）</t>
         </is>
       </c>
       <c r="D12" s="4" t="n">
@@ -738,7 +726,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>① M-17 SR-1 引込 屋外PB～冷媒管共巻き a×2・b×3・c×3</t>
+          <t>e 遠隔監視アダプタ電源（冷媒管共巻き）</t>
         </is>
       </c>
     </row>
@@ -750,25 +738,25 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>プルボックス250×250×200</t>
+          <t>電線管　E25</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>錆止め（SR-1引込 屋内側）</t>
+          <t>EP-25 屋内露出（SR-2立下り）</t>
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>個</t>
+          <t>ｍ</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>⑤ M-17 SR-1 引込 屋内側</t>
+          <t>③ M-18 SR-2 立下り</t>
         </is>
       </c>
     </row>
@@ -780,25 +768,25 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>機械はつり</t>
+          <t>電線管　E63</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>φ100 200mm（SR-1引込）</t>
+          <t>EP-63 屋内露出（SR-1引込）</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>か所</t>
+          <t>ｍ</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>⑥ M-17 ★印 SR-1 引込</t>
+          <t>② M-17 SR-1 引込 屋内PB～SR-1 a×2・b×3・c×3</t>
         </is>
       </c>
     </row>
@@ -810,42 +798,42 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>防水プルボックス300×300×200SUS</t>
+          <t>溶融亜鉛メッキ電線管　G70</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>屋外側（SR-1引込）</t>
+          <t>GP-70 屋外露出（SR-1引込）</t>
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>個</t>
+          <t>ｍ</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>④ M-17 SR-1 引込 屋外側</t>
+          <t>① M-17 SR-1 引込 屋外PB～冷媒管共巻き a×2・b×3・c×3</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>別途</t>
+          <t>電線管・ボックス</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>空調制御盤</t>
+          <t>プルボックス250×250×200</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>（別途）</t>
+          <t>錆止め（SR-1引込 屋内側）</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
@@ -853,29 +841,29 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>式</t>
+          <t>個</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>SR-1・SR-2（Kの指示で別途）</t>
+          <t>⑤ M-17 SR-1 引込 屋内側</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>別途</t>
+          <t>電線管・ボックス</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>計装試験調整</t>
+          <t>機械はつり</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>（別途）</t>
+          <t>φ100 200mm（SR-1引込）</t>
         </is>
       </c>
       <c r="D17" s="4" t="n">
@@ -883,12 +871,42 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>式</t>
+          <t>か所</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Kの指示で別途</t>
+          <t>⑥ M-17 ★印 SR-1 引込</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>電線管・ボックス</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>防水プルボックス300×300×200SUS</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>屋外側（SR-1引込）</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>個</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>④ M-17 SR-1 引込 屋外側</t>
         </is>
       </c>
     </row>

--- a/見積/数量表_大藪小_計装設備.xlsx
+++ b/見積/数量表_大藪小_計装設備.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -653,7 +653,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>ころがし（冷媒管共巻き・天井内）</t>
+          <t>管内（室外機置場）</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
@@ -666,7 +666,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>f 自立信号線</t>
+          <t>f 自立信号線（全長 M-20 の G36 内）</t>
         </is>
       </c>
     </row>
@@ -713,7 +713,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>ころがし（冷媒管共巻き・天井内）</t>
+          <t>管内（室外機置場）</t>
         </is>
       </c>
       <c r="D12" s="4" t="n">
@@ -726,7 +726,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>e 遠隔監視アダプタ電源（冷媒管共巻き）</t>
+          <t>e 遠隔監視アダプタ電源（全長 M-20 の G22 内）</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>③ M-18 SR-2 立下り</t>
+          <t>① M-18 SR-2 立下り</t>
         </is>
       </c>
     </row>
@@ -773,11 +773,11 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>EP-63 屋内露出（SR-1引込）</t>
+          <t>EP-63 床下（SR-1引込）</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>② M-17 SR-1 引込 屋内PB～SR-1 a×2・b×3・c×3</t>
+          <t>② M-17 SR-1 下～床下～外壁 a×2・b×3・c×3</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>GP-70 屋外露出（SR-1引込）</t>
+          <t>GP-70 屋外露出（SR-1立上り）</t>
         </is>
       </c>
       <c r="D15" s="4" t="n">
@@ -816,7 +816,7 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>① M-17 SR-1 引込 屋外PB～冷媒管共巻き a×2・b×3・c×3</t>
+          <t>③ M-17 外壁を抜いた後～冷媒管まで立上り</t>
         </is>
       </c>
     </row>
@@ -828,25 +828,25 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>プルボックス250×250×200</t>
+          <t>溶融亜鉛メッキ電線管　G22</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>錆止め（SR-1引込 屋内側）</t>
+          <t>GP-22 屋外露出（室外機置場）</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>個</t>
+          <t>ｍ</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>⑤ M-17 SR-1 引込 屋内側</t>
+          <t>④ M-20 d・e GHP-1～遠隔監視アダプタ</t>
         </is>
       </c>
     </row>
@@ -858,25 +858,25 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>機械はつり</t>
+          <t>溶融亜鉛メッキ電線管　G28</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>φ100 200mm（SR-1引込）</t>
+          <t>GP-28 屋外露出（室外機置場）</t>
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>か所</t>
+          <t>ｍ</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>⑥ M-17 ★印 SR-1 引込</t>
+          <t>⑤ M-20 a・d・h 置場入口～GHP-1～4</t>
         </is>
       </c>
     </row>
@@ -888,25 +888,85 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
+          <t>溶融亜鉛メッキ電線管　G36</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>GP-36 屋外露出（室外機置場）</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>ｍ</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>⑥ M-20 f・g 自立ユニット～GHP-1～4</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>電線管・ボックス</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>機械はつり</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>φ100 200mm（SR-1 外壁貫通）</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>か所</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>⑦ M-17 ★印 床下から外へ</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>電線管・ボックス</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
           <t>防水プルボックス300×300×200SUS</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>屋外側（SR-1引込）</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>屋外（SR-1立上り上部）</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>個</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>④ M-17 SR-1 引込 屋外側</t>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>⑧ M-17 立上り上部（ここから冷媒管共巻き）</t>
         </is>
       </c>
     </row>

--- a/見積/数量表_大藪小_計装設備.xlsx
+++ b/見積/数量表_大藪小_計装設備.xlsx
@@ -803,11 +803,11 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>GP-70 屋外露出（SR-1立上り）</t>
+          <t>GP-70 屋外露出（SR-1立上り・置場～天井裏）</t>
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>③ M-17 外壁を抜いた後～冷媒管まで立上り</t>
+          <t>③ M-17 SR-1 外壁を抜いた後～冷媒管 2.5m＋M-19/20 置場入口～建物～天井裏 5.5m（a×2・c×3・h×4）</t>
         </is>
       </c>
     </row>
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>⑥ M-20 f・g 自立ユニット～GHP-1～4</t>
+          <t>⑥ M-20 f・g 自立ユニット～GHP-1～4 15m＋c×3 自立ユニット～置場入口 7.76m</t>
         </is>
       </c>
     </row>
@@ -923,11 +923,11 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>φ100 200mm（SR-1 外壁貫通）</t>
+          <t>φ100 200mm（外壁貫通）</t>
         </is>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>⑦ M-17 ★印 床下から外へ</t>
+          <t>⑦ M-17 SR-1 床下から外へ・M-19 天井裏へ</t>
         </is>
       </c>
     </row>
@@ -953,11 +953,11 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>屋外（SR-1立上り上部）</t>
+          <t>屋外（立上り上部）</t>
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>⑧ M-17 立上り上部（ここから冷媒管共巻き）</t>
+          <t>⑧ M-17 SR-1 立上り上部・M-19 天井裏への立上り上部</t>
         </is>
       </c>
     </row>

--- a/見積/数量表_大藪小_計装設備.xlsx
+++ b/見積/数量表_大藪小_計装設備.xlsx
@@ -524,7 +524,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>輪之内中 2,877,000×0.65（Kの指示で輪之内中と同額）</t>
+          <t>三景電機 見積 R8.10.19（Kの指示で金額そのまま）</t>
         </is>
       </c>
     </row>
@@ -550,7 +550,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>輪之内中 2,731,000×0.65（Kの指示で輪之内中と同額）</t>
+          <t>三景電機 見積 R8.10.19（Kの指示で金額そのまま）</t>
         </is>
       </c>
     </row>
